--- a/test_scripts/осадка грунта v2.xlsx
+++ b/test_scripts/осадка грунта v2.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0F0A6E-92F4-421B-BDEC-7DFE0DE8D3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -127,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +143,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="13">
@@ -233,13 +242,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -256,6 +264,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -574,7 +585,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -701,7 +711,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -782,7 +791,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -790,6 +798,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -873,7 +882,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2547,7 +2555,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>513575</xdr:colOff>
+      <xdr:colOff>180200</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>105670</xdr:rowOff>
     </xdr:to>
@@ -2847,8 +2855,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2865,40 +2873,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="H1" s="5" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="O1" s="9" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="O1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="5">
+      <c r="P1" s="8"/>
+      <c r="Q1" s="4">
         <v>1</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="5"/>
+      <c r="T1" s="4"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2937,10 +2945,10 @@
       <c r="P2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>2</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <f>0</f>
         <v>0</v>
       </c>
@@ -2948,7 +2956,7 @@
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="T2" s="5"/>
+      <c r="T2" s="4"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2966,7 +2974,7 @@
         <f>1.8</f>
         <v>1.8</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <f>$D3*9.8*1000</f>
         <v>17640</v>
       </c>
@@ -2974,15 +2982,15 @@
         <f>11</f>
         <v>11</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <f t="shared" ref="H3:H10" si="0">2*C3/B$14</f>
         <v>0.4755244755244763</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="16">
         <f>-0.0002*($H3^4) + 0.0058*($H3^3)-0.0516*($H3^2)-0.0746*$H3+0.9781</f>
         <v>0.93157133194661734</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <f>$G$44</f>
         <v>0.95887412587412568</v>
       </c>
@@ -3006,7 +3014,7 @@
         <f>10</f>
         <v>10</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3" s="4">
         <v>3</v>
       </c>
       <c r="R3">
@@ -3017,10 +3025,10 @@
         <f>0.977</f>
         <v>0.97699999999999998</v>
       </c>
-      <c r="T3" s="5"/>
+      <c r="T3" s="4"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="1">
@@ -3035,7 +3043,7 @@
         <f>1.89</f>
         <v>1.89</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <f t="shared" ref="E4:E10" si="2">$D4*9.8*1000</f>
         <v>18522.000000000004</v>
       </c>
@@ -3043,15 +3051,15 @@
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <f t="shared" si="0"/>
         <v>0.66853146853146861</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="16">
         <f t="shared" ref="I4:I10" si="3">-0.0002*($H4^4) + 0.0058*($H4^3)-0.0516*($H4^2)-0.0746*$H4+0.9781</f>
         <v>0.90685877127896419</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="15">
         <f>I44</f>
         <v>0.91255244755244758</v>
       </c>
@@ -3059,7 +3067,7 @@
         <f>$C4-$C3</f>
         <v>1.3799999999999955</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>4</v>
       </c>
       <c r="R4">
@@ -3070,10 +3078,10 @@
         <f>0.881</f>
         <v>0.88100000000000001</v>
       </c>
-      <c r="T4" s="5"/>
+      <c r="T4" s="4"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="1">
@@ -3088,7 +3096,7 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <f t="shared" si="2"/>
         <v>19012</v>
       </c>
@@ -3096,15 +3104,15 @@
         <f>6.1</f>
         <v>6.1</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <f t="shared" si="0"/>
         <v>0.82237762237762169</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <f t="shared" si="3"/>
         <v>0.88498764882450054</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="15">
         <f>K44</f>
         <v>0.87395104895104914</v>
       </c>
@@ -3112,7 +3120,7 @@
         <f t="shared" ref="M5:M6" si="5">$C5-$C4</f>
         <v>1.0999999999999943</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>5</v>
       </c>
       <c r="R5">
@@ -3123,10 +3131,10 @@
         <f>0.755</f>
         <v>0.755</v>
       </c>
-      <c r="T5" s="5"/>
+      <c r="T5" s="4"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
       <c r="B6" s="1">
@@ -3141,7 +3149,7 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <f t="shared" si="2"/>
         <v>19012</v>
       </c>
@@ -3149,15 +3157,15 @@
         <f>6.1</f>
         <v>6.1</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <f t="shared" si="0"/>
         <v>0.86853146853146757</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="16">
         <f t="shared" si="3"/>
         <v>0.87806945332493436</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <f>M44</f>
         <v>0.85941258741258775</v>
       </c>
@@ -3165,7 +3173,7 @@
         <f t="shared" si="5"/>
         <v>0.32999999999999829</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="4">
         <v>6</v>
       </c>
       <c r="R6">
@@ -3176,10 +3184,10 @@
         <f>0.642</f>
         <v>0.64200000000000002</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="T6" s="4"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="1">
@@ -3194,22 +3202,22 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <f t="shared" si="2"/>
         <v>19012</v>
       </c>
       <c r="F7" s="1">
         <v>4.5</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <f t="shared" si="0"/>
         <v>1.7314685314685307</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <f t="shared" si="3"/>
         <v>0.72254622925057843</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <f>G47</f>
         <v>0.61176223776223793</v>
       </c>
@@ -3217,7 +3225,7 @@
         <f>$C7-$C5</f>
         <v>6.5</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
         <v>7</v>
       </c>
       <c r="R7">
@@ -3228,10 +3236,10 @@
         <f>0.55</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="T7" s="5"/>
+      <c r="T7" s="4"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>4</v>
       </c>
       <c r="B8" s="1">
@@ -3246,22 +3254,22 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <f t="shared" si="2"/>
         <v>19012</v>
       </c>
       <c r="F8" s="1">
         <v>6.1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <f t="shared" si="0"/>
         <v>2.3986013986013992</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <f t="shared" si="3"/>
         <v>0.57571368246578891</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <f>I47</f>
         <v>0.47725524475524461</v>
       </c>
@@ -3269,7 +3277,7 @@
         <f>$C8-$C7</f>
         <v>4.7700000000000102</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="4">
         <v>8</v>
       </c>
       <c r="R8">
@@ -3280,10 +3288,10 @@
         <f>0.477</f>
         <v>0.47699999999999998</v>
       </c>
-      <c r="T8" s="5"/>
+      <c r="T8" s="4"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>3</v>
       </c>
       <c r="B9" s="1">
@@ -3298,7 +3306,7 @@
         <f>1.89</f>
         <v>1.89</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9">
         <f t="shared" si="2"/>
         <v>18522.000000000004</v>
       </c>
@@ -3306,15 +3314,15 @@
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <f t="shared" si="0"/>
         <v>3.5818181818181816</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <f t="shared" si="3"/>
         <v>0.28250480358445462</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <f>K47</f>
         <v>0.33868181818181819</v>
       </c>
@@ -3322,7 +3330,7 @@
         <f>$C9-$C8</f>
         <v>8.4599999999999937</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="4">
         <v>9</v>
       </c>
       <c r="R9">
@@ -3333,10 +3341,10 @@
         <f>0.42</f>
         <v>0.42</v>
       </c>
-      <c r="T9" s="5"/>
+      <c r="T9" s="4"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -3351,22 +3359,22 @@
         <f>1.97</f>
         <v>1.97</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
         <f t="shared" si="2"/>
         <v>19306</v>
       </c>
       <c r="F10" s="1">
         <v>11.2</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <f t="shared" si="0"/>
         <v>4.4349650349650336</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="16">
         <f t="shared" si="3"/>
         <v>6.0901867358512995E-2</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="15">
         <f>M47</f>
         <v>0.27807692307692317</v>
       </c>
@@ -3374,7 +3382,7 @@
         <f>$C10-$C9</f>
         <v>6.0999999999999943</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>10</v>
       </c>
       <c r="R10">
@@ -3385,10 +3393,10 @@
         <f>0.374</f>
         <v>0.374</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="4"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q11" s="5">
+      <c r="Q11" s="4">
         <v>11</v>
       </c>
       <c r="R11">
@@ -3399,19 +3407,19 @@
         <f>0.337</f>
         <v>0.33700000000000002</v>
       </c>
-      <c r="T11" s="5"/>
+      <c r="T11" s="4"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="4">
         <v>12</v>
       </c>
       <c r="R12">
@@ -3422,7 +3430,7 @@
         <f>0.306</f>
         <v>0.30599999999999999</v>
       </c>
-      <c r="T12" s="5"/>
+      <c r="T12" s="4"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -3438,7 +3446,7 @@
         <f>10^6</f>
         <v>1000000</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="Q13" s="4">
         <v>13</v>
       </c>
       <c r="R13">
@@ -3449,7 +3457,7 @@
         <f>0.28</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="4"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3464,21 +3472,21 @@
         <f>160000</f>
         <v>160000</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="Q14" s="4">
         <v>14</v>
       </c>
       <c r="R14">
         <f t="shared" ref="R14:R31" si="6">R13+0.4</f>
         <v>4.8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14">
         <f>0.258</f>
         <v>0.25800000000000001</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="T14" s="4"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q15" s="5">
+      <c r="Q15" s="4">
         <v>15</v>
       </c>
       <c r="R15">
@@ -3488,10 +3496,10 @@
       <c r="S15">
         <v>0.23899999999999999</v>
       </c>
-      <c r="T15" s="5"/>
+      <c r="T15" s="4"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q16" s="5">
+      <c r="Q16" s="4">
         <v>16</v>
       </c>
       <c r="R16">
@@ -3501,10 +3509,10 @@
       <c r="S16">
         <v>0.223</v>
       </c>
-      <c r="T16" s="5"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Q17" s="5">
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q17" s="4">
         <v>17</v>
       </c>
       <c r="R17">
@@ -3514,10 +3522,10 @@
       <c r="S17">
         <v>0.20799999999999999</v>
       </c>
-      <c r="T17" s="5"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Q18" s="5">
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q18" s="4">
         <v>18</v>
       </c>
       <c r="R18">
@@ -3527,10 +3535,10 @@
       <c r="S18">
         <v>0.19600000000000001</v>
       </c>
-      <c r="T18" s="5"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Q19" s="5">
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q19" s="4">
         <v>19</v>
       </c>
       <c r="R19">
@@ -3540,22 +3548,22 @@
       <c r="S19">
         <v>0.185</v>
       </c>
-      <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="T19" s="4"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="G20" s="5" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="G20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q20" s="5">
+      <c r="Q20" s="4">
         <v>20</v>
       </c>
       <c r="R20">
@@ -3565,16 +3573,16 @@
       <c r="S20">
         <v>0.17499999999999999</v>
       </c>
-      <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3586,7 +3594,7 @@
       <c r="H21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q21" s="5">
+      <c r="Q21" s="4">
         <v>21</v>
       </c>
       <c r="R21">
@@ -3596,9 +3604,9 @@
       <c r="S21">
         <v>0.16600000000000001</v>
       </c>
-      <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f>0</f>
         <v>0</v>
@@ -3623,7 +3631,7 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="5">
+      <c r="Q22" s="4">
         <v>22</v>
       </c>
       <c r="R22">
@@ -3633,8 +3641,8 @@
       <c r="S22">
         <v>0.158</v>
       </c>
-      <c r="T22" s="5"/>
-      <c r="V22" s="5" t="s">
+      <c r="T22" s="4"/>
+      <c r="V22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="W22" s="2" t="s">
@@ -3646,9 +3654,8 @@
       <c r="Y22" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="Z22" s="3"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" ref="A23:A30" si="7">C3</f>
         <v>3.4000000000000057</v>
@@ -3673,7 +3680,7 @@
         <f t="shared" ref="H23:H30" si="10">$A$14*((B23*M3)/B3)</f>
         <v>3.7936547234583652E-2</v>
       </c>
-      <c r="Q23" s="5">
+      <c r="Q23" s="4">
         <v>23</v>
       </c>
       <c r="R23">
@@ -3683,7 +3690,7 @@
       <c r="S23">
         <v>0.15</v>
       </c>
-      <c r="T23" s="5"/>
+      <c r="T23" s="4"/>
       <c r="V23" s="2" t="s">
         <v>8</v>
       </c>
@@ -3699,9 +3706,8 @@
         <f>1.8</f>
         <v>1.8</v>
       </c>
-      <c r="Z23" s="3"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="7"/>
         <v>4.7800000000000011</v>
@@ -3726,7 +3732,7 @@
         <f t="shared" si="10"/>
         <v>2.3027609190809119E-2</v>
       </c>
-      <c r="Q24" s="5">
+      <c r="Q24" s="4">
         <v>24</v>
       </c>
       <c r="R24">
@@ -3736,8 +3742,8 @@
       <c r="S24">
         <v>0.14299999999999999</v>
       </c>
-      <c r="T24" s="5"/>
-      <c r="V24" s="4">
+      <c r="T24" s="4"/>
+      <c r="V24" s="3">
         <v>3</v>
       </c>
       <c r="W24" s="1">
@@ -3752,9 +3758,8 @@
         <f>1.89</f>
         <v>1.89</v>
       </c>
-      <c r="Z24" s="3"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="7"/>
         <v>5.8799999999999955</v>
@@ -3779,7 +3784,7 @@
         <f>$A$14*((B25*M5)/B5)</f>
         <v>2.0172509457755259E-2</v>
       </c>
-      <c r="Q25" s="5">
+      <c r="Q25" s="4">
         <v>25</v>
       </c>
       <c r="R25">
@@ -3789,8 +3794,8 @@
       <c r="S25">
         <v>0.13700000000000001</v>
       </c>
-      <c r="T25" s="5"/>
-      <c r="V25" s="4">
+      <c r="T25" s="4"/>
+      <c r="V25" s="3">
         <v>4</v>
       </c>
       <c r="W25" s="1">
@@ -3805,10 +3810,9 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="Z25" s="3"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
         <f t="shared" si="7"/>
         <v>6.2099999999999937</v>
       </c>
@@ -3832,7 +3836,7 @@
         <f t="shared" si="10"/>
         <v>5.9510799495586103E-3</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q26" s="4">
         <v>26</v>
       </c>
       <c r="R26">
@@ -3842,8 +3846,8 @@
       <c r="S26">
         <v>0.13200000000000001</v>
       </c>
-      <c r="T26" s="5"/>
-      <c r="V26" s="4">
+      <c r="T26" s="4"/>
+      <c r="V26" s="3">
         <v>5</v>
       </c>
       <c r="W26" s="1">
@@ -3858,10 +3862,9 @@
         <f>1.94</f>
         <v>1.94</v>
       </c>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
         <f t="shared" si="7"/>
         <v>12.379999999999995</v>
       </c>
@@ -3885,7 +3888,7 @@
         <f t="shared" si="10"/>
         <v>0.11310804040404046</v>
       </c>
-      <c r="Q27" s="5">
+      <c r="Q27" s="4">
         <v>27</v>
       </c>
       <c r="R27">
@@ -3895,8 +3898,8 @@
       <c r="S27">
         <v>0.126</v>
       </c>
-      <c r="T27" s="5"/>
-      <c r="V27" s="4">
+      <c r="T27" s="4"/>
+      <c r="V27" s="3">
         <v>6</v>
       </c>
       <c r="W27" s="1"/>
@@ -3905,10 +3908,9 @@
         <v>17.150000000000006</v>
       </c>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="3"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
         <f t="shared" si="7"/>
         <v>17.150000000000006</v>
       </c>
@@ -3924,15 +3926,15 @@
         <f t="shared" si="12"/>
         <v>326988.76000000007</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <f t="shared" si="9"/>
         <v>4.7769338071764391</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="18">
         <f t="shared" si="10"/>
         <v>4.7769338071764395E-2</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q28" s="4">
         <v>28</v>
       </c>
       <c r="R28">
@@ -3942,8 +3944,8 @@
       <c r="S28">
         <v>0.122</v>
       </c>
-      <c r="T28" s="5"/>
-      <c r="V28" s="4">
+      <c r="T28" s="4"/>
+      <c r="V28" s="3">
         <v>7</v>
       </c>
       <c r="W28" s="1">
@@ -3957,10 +3959,9 @@
         <f>1.97</f>
         <v>1.97</v>
       </c>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
         <f t="shared" si="7"/>
         <v>25.61</v>
       </c>
@@ -3984,7 +3985,7 @@
         <f t="shared" si="10"/>
         <v>5.2393109610389579E-2</v>
       </c>
-      <c r="Q29" s="5">
+      <c r="Q29" s="4">
         <v>29</v>
       </c>
       <c r="R29">
@@ -3994,10 +3995,10 @@
       <c r="S29">
         <v>0.11700000000000001</v>
       </c>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="T29" s="4"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <f t="shared" si="7"/>
         <v>31.709999999999994</v>
       </c>
@@ -4021,7 +4022,7 @@
         <f t="shared" si="10"/>
         <v>1.9385934065934057E-2</v>
       </c>
-      <c r="Q30" s="5">
+      <c r="Q30" s="4">
         <v>30</v>
       </c>
       <c r="R30">
@@ -4031,18 +4032,18 @@
       <c r="S30">
         <v>0.113</v>
       </c>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G31" s="10">
+      <c r="T30" s="4"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G31" s="9">
         <f>SUM(G22:G27)</f>
         <v>20.019578623674711</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <f>SUM(H22:H27)</f>
         <v>0.20019578623674711</v>
       </c>
-      <c r="Q31" s="5">
+      <c r="Q31" s="4">
         <v>31</v>
       </c>
       <c r="R31">
@@ -4052,10 +4053,10 @@
       <c r="S31">
         <v>0.109</v>
       </c>
-      <c r="T31" s="5"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Q32" s="5">
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q32" s="4">
         <v>32</v>
       </c>
       <c r="R32">
@@ -4065,30 +4066,30 @@
       <c r="S32">
         <v>0.106</v>
       </c>
-      <c r="T32" s="5"/>
+      <c r="T32" s="4"/>
     </row>
     <row r="33" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
     </row>
     <row r="42" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E42" s="15"/>
-      <c r="F42" s="15" t="s">
+      <c r="E42" s="14"/>
+      <c r="F42" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
     </row>
     <row r="43" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E43" s="15"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="2">
         <f>R3</f>
         <v>0.4</v>
@@ -4121,15 +4122,15 @@
         <f>S4</f>
         <v>0.88100000000000001</v>
       </c>
-      <c r="N43" s="15"/>
+      <c r="N43" s="14"/>
     </row>
     <row r="44" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E44" s="15"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="2">
         <f>$H$3</f>
         <v>0.4755244755244763</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="13">
         <f>((G45-G43)/(F45-F43))*(F44-F43)+G43</f>
         <v>0.95887412587412568</v>
       </c>
@@ -4137,7 +4138,7 @@
         <f>$H$4</f>
         <v>0.66853146853146861</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="4">
         <f>((I45-I43)/(H45-H43))*(H44-H43)+I43</f>
         <v>0.91255244755244758</v>
       </c>
@@ -4145,7 +4146,7 @@
         <f>$H$5</f>
         <v>0.82237762237762169</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="13">
         <f>((K45-K43)/(J45-J43))*(J44-J43)+K43</f>
         <v>0.87395104895104914</v>
       </c>
@@ -4153,14 +4154,14 @@
         <f>$H$6</f>
         <v>0.86853146853146757</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="4">
         <f>((M45-M43)/(L45-L43))*(L44-L43)+M43</f>
         <v>0.85941258741258775</v>
       </c>
-      <c r="N44" s="15"/>
+      <c r="N44" s="14"/>
     </row>
     <row r="45" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E45" s="15"/>
+      <c r="E45" s="14"/>
       <c r="F45" s="2">
         <f>R4</f>
         <v>0.8</v>
@@ -4193,10 +4194,10 @@
         <f>S5</f>
         <v>0.755</v>
       </c>
-      <c r="N45" s="15"/>
+      <c r="N45" s="14"/>
     </row>
     <row r="46" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E46" s="15"/>
+      <c r="E46" s="14"/>
       <c r="F46" s="1">
         <f>R6</f>
         <v>1.6</v>
@@ -4229,15 +4230,15 @@
         <f>S13</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="15"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E47" s="15"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="1">
         <f>$H$7</f>
         <v>1.7314685314685307</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="4">
         <f>((G48-G46)/(F48-F46))*(F47-F46)+G46</f>
         <v>0.61176223776223793</v>
       </c>
@@ -4245,7 +4246,7 @@
         <f>$H$8</f>
         <v>2.3986013986013992</v>
       </c>
-      <c r="I47" s="14">
+      <c r="I47" s="13">
         <f>((I48-I46)/(H48-H46))*(H47-H46)+I46</f>
         <v>0.47725524475524461</v>
       </c>
@@ -4253,7 +4254,7 @@
         <f>$H$9</f>
         <v>3.5818181818181816</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="4">
         <f>((K48-K46)/(J48-J46))*(J47-J46)+K46</f>
         <v>0.33868181818181819</v>
       </c>
@@ -4261,14 +4262,14 @@
         <f>$H$10</f>
         <v>4.4349650349650336</v>
       </c>
-      <c r="M47" s="14">
+      <c r="M47" s="13">
         <f>((M48-M46)/(L48-L46))*(L47-L46)+M46</f>
         <v>0.27807692307692317</v>
       </c>
-      <c r="N47" s="15"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" spans="5:20" x14ac:dyDescent="0.25">
-      <c r="E48" s="15"/>
+      <c r="E48" s="14"/>
       <c r="F48" s="1">
         <f>R7</f>
         <v>2</v>
@@ -4301,19 +4302,19 @@
         <f>S14</f>
         <v>0.25800000000000001</v>
       </c>
-      <c r="N48" s="15"/>
+      <c r="N48" s="14"/>
     </row>
     <row r="49" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4323,15 +4324,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
@@ -4352,7 +4356,7 @@
         <f>0.8</f>
         <v>0.8</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <f>0.848</f>
         <v>0.84799999999999998</v>
       </c>
@@ -4360,7 +4364,7 @@
         <f>((D3-B3)/(D$2-B$2))*(C$2-B$2)+B3</f>
         <v>0.85699999999999998</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <f>0.866</f>
         <v>0.86599999999999999</v>
       </c>
@@ -4380,7 +4384,7 @@
         <f>A3+0.4</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f>0.682</f>
         <v>0.68200000000000005</v>
       </c>
@@ -4388,14 +4392,48 @@
         <f t="shared" si="0"/>
         <v>0.69950000000000001</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f>0.717</f>
         <v>0.71699999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F38" s="19">
+        <v>0.13986000000000001</v>
+      </c>
+      <c r="G38" s="13">
+        <f>((G39-G37)/(F39-F37))*(F38-F37)+G37</f>
+        <v>0.95839165000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F39" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0.88100000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F0B23B-72FC-4375-949B-9253CBD53B88}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
